--- a/artfynd/A 37275-2026 artfynd.xlsx
+++ b/artfynd/A 37275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583085</v>
       </c>
       <c r="B2" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37275-2026 artfynd.xlsx
+++ b/artfynd/A 37275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583085</v>
       </c>
       <c r="B2" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37275-2026 artfynd.xlsx
+++ b/artfynd/A 37275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583085</v>
       </c>
       <c r="B2" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37275-2026 artfynd.xlsx
+++ b/artfynd/A 37275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583085</v>
       </c>
       <c r="B2" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37275-2026 artfynd.xlsx
+++ b/artfynd/A 37275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583085</v>
       </c>
       <c r="B2" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37275-2026 artfynd.xlsx
+++ b/artfynd/A 37275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583085</v>
       </c>
       <c r="B2" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37275-2026 artfynd.xlsx
+++ b/artfynd/A 37275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583085</v>
       </c>
       <c r="B2" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37275-2026 artfynd.xlsx
+++ b/artfynd/A 37275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583085</v>
       </c>
       <c r="B2" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37275-2026 artfynd.xlsx
+++ b/artfynd/A 37275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583085</v>
       </c>
       <c r="B2" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37275-2026 artfynd.xlsx
+++ b/artfynd/A 37275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583085</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37275-2026 artfynd.xlsx
+++ b/artfynd/A 37275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583085</v>
       </c>
       <c r="B2" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
